--- a/Delhi-December-2025.xlsx
+++ b/Delhi-December-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="88">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Delhi</t>
   </si>
   <si>
@@ -106,10 +109,10 @@
     <t>MH02FG7557</t>
   </si>
   <si>
-    <t>DL1NA-3869</t>
-  </si>
-  <si>
-    <t>DL1NA-3910</t>
+    <t>DL1NA3869</t>
+  </si>
+  <si>
+    <t>DL1NA3910</t>
   </si>
   <si>
     <t>HR38AD1176</t>
@@ -127,10 +130,10 @@
     <t>HR38AE5738</t>
   </si>
   <si>
-    <t>HR55AR-0857</t>
-  </si>
-  <si>
-    <t>HR55AR-1793</t>
+    <t>HR55AR0857</t>
+  </si>
+  <si>
+    <t>HR55AR1793</t>
   </si>
   <si>
     <t>MH02ER7925</t>
@@ -154,13 +157,13 @@
     <t>HR55AU6270</t>
   </si>
   <si>
-    <t>MH02FG 4112</t>
-  </si>
-  <si>
-    <t>MH02FG 7817</t>
-  </si>
-  <si>
-    <t>MH02FG 0905</t>
+    <t>MH02FG4112</t>
+  </si>
+  <si>
+    <t>MH02FG7817</t>
+  </si>
+  <si>
+    <t>MH02FG0905</t>
   </si>
   <si>
     <t>MH02GH0253</t>
@@ -175,7 +178,7 @@
     <t>HR55AX5016</t>
   </si>
   <si>
-    <t>DL1N-6505</t>
+    <t>DL1N6505</t>
   </si>
   <si>
     <t>HR38AE9224</t>
@@ -211,7 +214,7 @@
     <t>CAMRY</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>HYCROSS</t>
@@ -235,31 +238,46 @@
     <t>25/01/2024</t>
   </si>
   <si>
+    <t>17/08/2022</t>
+  </si>
+  <si>
+    <t>21/04/2023</t>
+  </si>
+  <si>
+    <t>28/11/2023</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>21/09/2021</t>
+  </si>
+  <si>
+    <t>21/10/2021</t>
+  </si>
+  <si>
+    <t>28/06/2022</t>
+  </si>
+  <si>
+    <t>16/09/2024</t>
+  </si>
+  <si>
+    <t>24/06/2025</t>
+  </si>
+  <si>
+    <t>21/04/2014</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>23/01/2025</t>
+  </si>
+  <si>
+    <t>30/07/2024</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>17/08/2022</t>
-  </si>
-  <si>
-    <t>21/04/2023</t>
-  </si>
-  <si>
-    <t>25/03/2021</t>
-  </si>
-  <si>
-    <t>21/09/2021</t>
-  </si>
-  <si>
-    <t>21/10/2021</t>
-  </si>
-  <si>
-    <t>14/03/2023</t>
-  </si>
-  <si>
-    <t>23/01/2025</t>
-  </si>
-  <si>
-    <t>30/07/2024</t>
   </si>
 </sst>
 </file>
@@ -621,10 +639,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,28 +721,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H2">
         <v>63288</v>
@@ -784,24 +805,24 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" s="2">
         <v>44748</v>
@@ -864,27 +885,27 @@
         <v>-288.22</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="G4" s="2">
+        <v>43565</v>
       </c>
       <c r="H4">
         <v>241453</v>
@@ -944,27 +965,27 @@
         <v>58.49</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="G5" s="2">
+        <v>43565</v>
       </c>
       <c r="H5">
         <v>238947</v>
@@ -1024,24 +1045,24 @@
         <v>59.89</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6" t="s">
         <v>74</v>
@@ -1104,24 +1125,24 @@
         <v>53.31</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7" s="2">
         <v>44904</v>
@@ -1184,24 +1205,24 @@
         <v>55.24</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
         <v>74</v>
@@ -1264,24 +1285,24 @@
         <v>39.14</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9" s="2">
         <v>44904</v>
@@ -1344,24 +1365,24 @@
         <v>55.37</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
         <v>75</v>
@@ -1424,27 +1445,27 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H11">
         <v>106548</v>
@@ -1504,27 +1525,27 @@
         <v>25.01</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H12">
         <v>126262</v>
@@ -1584,27 +1605,27 @@
         <v>26.35</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="G13" s="2">
+        <v>43587</v>
       </c>
       <c r="H13">
         <v>199905</v>
@@ -1664,24 +1685,24 @@
         <v>53.93</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2">
         <v>44441</v>
@@ -1744,27 +1765,27 @@
         <v>50.11</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H15">
         <v>110061</v>
@@ -1824,27 +1845,27 @@
         <v>51.52</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16">
         <v>113428</v>
@@ -1909,22 +1930,22 @@
         <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17">
         <v>104237</v>
@@ -1989,19 +2010,19 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2">
         <v>44629</v>
@@ -2069,19 +2090,19 @@
         <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" s="2">
         <v>45331</v>
@@ -2149,22 +2170,22 @@
         <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="G20" s="2">
+        <v>44471</v>
       </c>
       <c r="H20">
         <v>77399</v>
@@ -2229,22 +2250,22 @@
         <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H21">
         <v>55267</v>
@@ -2309,22 +2330,22 @@
         <v>94</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H22">
         <v>12887</v>
@@ -2386,19 +2407,19 @@
         <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2">
         <v>45634</v>
@@ -2466,19 +2487,19 @@
         <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2">
         <v>45323</v>
@@ -2543,22 +2564,22 @@
         <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H25">
         <v>20672</v>
@@ -2623,22 +2644,22 @@
         <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H26">
         <v>14629</v>
@@ -2703,22 +2724,22 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2772,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="Z27" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:26">
@@ -2780,22 +2801,22 @@
         <v>100</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H28">
         <v>107883</v>
@@ -2860,19 +2881,19 @@
         <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2">
         <v>45451</v>
@@ -2940,19 +2961,19 @@
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2">
         <v>45451</v>
@@ -3020,19 +3041,19 @@
         <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2">
         <v>45511</v>
@@ -3100,19 +3121,19 @@
         <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G32" s="2">
         <v>45511</v>
@@ -3180,22 +3201,22 @@
         <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H33">
         <v>18429</v>
@@ -3260,22 +3281,22 @@
         <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H34">
         <v>87885</v>
@@ -3340,22 +3361,22 @@
         <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H35">
         <v>76264</v>
@@ -3420,22 +3441,22 @@
         <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G36" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H36">
         <v>71314</v>
